--- a/data_extactor/batch_10_fa/trimmed/batch_0042_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0042_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مخابرات | کامپیوتر و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مهندسی و فناوری | هنرهای تجسمی و نمایشی | خدمات مشتریان و خدمات فردی</t>
+          <t>مخابرات | رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مهندسی و فناوری | هنرهای زیبا | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های صوت و تصویر | تکنسین‌های پخش | تکنسین‌های صدابرداری و مهندسی صدا | تکنسین‌های نورپردازی | تصویربرداران تلویزیون، ویدئو و سینما | تدوین‌گران فیلم و ویدئو | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز نصابان خطوط ارتباطی</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | تکنسین‌های مهندسی صدا | تکنسین‌های نورپردازی | تصویربرداران تلویزیون، ویدیو و سینما | تدوین‌گران فیلم و ویدیو | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | علوم تجربی و پایه | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | علوم | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | روان‌شناسی | مدیریت و امور اداری | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زیست‌شناسی | روان‌شناسی | مدیریت و اداره | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | پزشکان عمومی و خانواده | پزشکان طب سنتی و طبیعی | متخصصان مغز و اعصاب (نورولوژیست) | جراحان ارتوپدی (به‌جز اطفال) | متخصصان طب فیزیکی و توان‌بخشی</t>
+          <t>متخصصان و کارشناسان طب سوزنی | پزشکان عمومی و خانواده | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | جراحان ارتوپدی، غیر از اطفال | متخصصان طب فیزیکی و توانبخشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | علوم تجربی و پایه | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | علوم | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | روان‌شناسی | آموزش و تدریس | مدیریت و امور اداری</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زیست‌شناسی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | حساسیت به مسئله | استدلال قیاسی | ثبات دست و بازو | دید نزدیک | درک شفاهی | دقت کنترل حرکتی</t>
+          <t>مهارت انگشتان | حساسیت به مسئله | استدلال قیاسی | ثبات دست و بازو | بینایی نزدیک | درک شفاهی | دقت کنترل</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>دستیاران دندان‌پزشک | کارشناسان بهداشت دهان و دندان | دستیاران پزشک | جراحان دهان، فک و صورت | متخصصان ارتودنسی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی</t>
+          <t>دستیاران دندان‌پزشک | بهداشت‌کاران دهان و دندان | کمک‌پزشکان و دستیاران مطب | جراحان دهان، فک و صورت | متخصصان ارتودنسی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | نگارش | علوم تجربی و پایه</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | نگارش | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | روان‌شناسی | آموزش و تدریس | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | شیمی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | دید نزدیک | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | دقت کنترل حرکتی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | دقت کنترل</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | دستیاران دندان‌پزشک | دندان‌پزشکان عمومی | متخصصان ارتودنسی | جراحان ارتوپدی (به‌جز اطفال) | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی</t>
+          <t>متخصصان بیهوشی | دستیاران دندان‌پزشک | دندان‌پزشکان عمومی | متخصصان ارتودنسی | جراحان ارتوپدی، غیر از اطفال | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | یادگیری فعال | نگارش | علوم تجربی و پایه | راهبردهای یادگیری</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | نگارش | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | کامپیوتر و الکترونیک | مدیریت و امور اداری | آموزش و تدریس</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زیست‌شناسی | رایانه و الکترونیک | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | ثبات دست و بازو | چابکی انگشتان</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | ثبات دست و بازو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>دستیاران دندان‌پزشک | کارشناسان بهداشت دهان و دندان | دندان‌پزشکان عمومی | جراحان دهان، فک و صورت | متخصصان پروتزهای دندانی (پروستودنتیست‌ها)</t>
+          <t>دستیاران دندان‌پزشک | بهداشت‌کاران دهان و دندان | دندان‌پزشکان عمومی | جراحان دهان، فک و صورت | متخصصان پروتزهای دندانی (پروستودنتیست‌ها)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم تجربی و پایه</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | زیست‌شناسی | آموزش و تدریس | روان‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک شفاهی | بیان شفاهی | استدلال قیاسی | چابکی انگشتان | ثبات دست و بازو</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک شفاهی | بیان شفاهی | استدلال قیاسی | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>دستیاران دندان‌پزشک | کارشناسان بهداشت دهان و دندان | تکنسین‌های پروتزهای دندانی (لابراتوار دندان‌سازی) | دندان‌پزشکان عمومی | جراحان دهان، فک و صورت | متخصصان ارتودنسی | متخصصان ساخت ارتوز و پروتز (اعضای مصنوعی)</t>
+          <t>دستیاران دندان‌پزشک | بهداشت‌کاران دهان و دندان | تکنسین‌های پروتزهای دندانی و لابراتوار دندانسازی | دندان‌پزشکان عمومی | جراحان دهان، فک و صورت | متخصصان ارتودنسی | ارتوپدهای فنی و سازندگان اعضای مصنوعی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم تجربی و پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتریان و خدمات فردی | روان‌شناسی | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | چابکی انگشتان</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دندان‌پزشکان عمومی | متخصصان ارتودنسی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | جراحان دهان، فک و صورت | کارشناسان بهداشت دهان و دندان | دستیاران دندان‌پزشک | دستیاران جراحی</t>
+          <t>دندان‌پزشکان عمومی | متخصصان ارتودنسی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | جراحان دهان، فک و صورت | بهداشت‌کاران دهان و دندان | دستیاران دندان‌پزشک | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال | علوم تجربی و پایه | ریاضیات</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | پزشکی و دندان‌پزشکی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | آموزش و تدریس | صنایع و تولید مواد غذایی</t>
+          <t>زیست‌شناسی | پزشکی و دندان‌پزشکی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش | تولید مواد غذایی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های تغذیه | فیزیولوژیست‌های ورزشی | پزشکان عمومی و خانواده | کارشناسان آموزش و ارتقای سلامت | کاردرمانگران | داروسازان | کارشناسان پرستاری (پرستاران رسمی)</t>
+          <t>کاردان‌ها و تکنسین‌های تغذیه و رژیم‌درمانی | فیزیولوژیست‌های ورزشی | پزشکان عمومی و خانواده | کارشناسان آموزش بهداشت و ارتقای سلامت | کاردرمانگران | داروسازان | پرستاران</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نگارش | علوم تجربی و پایه | نظارت | راهبردهای یادگیری | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | علوم | نظارت | راهبردهای یادگیری | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | ریاضیات | درمان و مشاوره | فیزیک</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | ریاضیات | درمان و مشاوره | فیزیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران دوره‌دیده مراقبت‌های پیشرفته | تکنسین‌های چشم‌پزشکی | کارشناسان فناوری‌های چشمی و بینایی‌سنجی | چشم‌پزشکان (به‌جز اطفال) | متخصصان کودکان و اطفال | متخصصان طب فیزیکی و توان‌بخشی</t>
+          <t>پرستاران بالینی پیشرفته | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی، غیر از اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | علوم تجربی و پایه | ریاضیات | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | علوم | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | ریاضیات | خدمات مشتریان و خدمات فردی | شیمی | زیست‌شناسی | کامپیوتر و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | ریاضیات | خدمات مشتری و شخصی | شیمی | زیست‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | دید نزدیک | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پزشکان عمومی و خانواده | متخصصان بیماری‌های داخلی | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | تکنسین‌های دارویی (نسخه‌پیچ‌ها) | متخصصان طب پیشگیری و پزشکی اجتماعی | کارشناسان پرستاری (پرستاران رسمی)</t>
+          <t>پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | تکنسین‌های داروخانه (نسخه‌پیچ‌ها) | متخصصان پزشکی اجتماعی و طب پیشگیری | پرستاران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
